--- a/Excel/data.xlsx
+++ b/Excel/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tihitinazergaw\Documents\DataAnalytics-2026\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C9D622F-0486-4257-B3BE-FD448C737F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E96D5B5F-FC29-488D-A6C7-4E1F02B92EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{385C3899-7CDD-44DE-81CB-A112167F8E31}"/>
   </bookViews>
